--- a/output/details/2026-05-18/preprocessed_data.xlsx
+++ b/output/details/2026-05-18/preprocessed_data.xlsx
@@ -15231,25 +15231,25 @@
         <v>46160</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.1107339469384084</v>
+        <v>-0.1126672987152823</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1634877692114839</v>
+        <v>-0.1397130247790246</v>
       </c>
       <c r="D2" t="n">
-        <v>0.163260131462705</v>
+        <v>-0.1394381721364216</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.1262785842928937</v>
+        <v>0.0001526552903121012</v>
       </c>
       <c r="F2" t="n">
-        <v>0.001701536716824397</v>
+        <v>0.001700030293259207</v>
       </c>
       <c r="G2" t="n">
-        <v>1.893258990806939</v>
+        <v>2.462686572122487</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.4465207781602148</v>
+        <v>-0.2667867875270903</v>
       </c>
       <c r="I2" t="n">
         <v>1</v>
